--- a/docs/source/tutorials/sequential_problems/materials/model/input_data/input_data.xlsx
+++ b/docs/source/tutorials/sequential_problems/materials/model/input_data/input_data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="supply_1" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="11">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -31,15 +31,24 @@
     <t xml:space="preserve">products_Name</t>
   </si>
   <si>
+    <t xml:space="preserve">values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cemento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ammoniaca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plastica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acciaio</t>
+  </si>
+  <si>
     <t xml:space="preserve">resources_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cemento</t>
-  </si>
-  <si>
     <t xml:space="preserve">tanto</t>
   </si>
   <si>
@@ -47,15 +56,6 @@
   </si>
   <si>
     <t xml:space="preserve">poco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ammoniaca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plastica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acciaio</t>
   </si>
 </sst>
 </file>
@@ -346,7 +346,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.4375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -359,19 +359,13 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -381,19 +375,13 @@
       <c r="B3" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -401,98 +389,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="0" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -522,7 +419,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -530,7 +427,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>1</v>
@@ -541,7 +438,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>2</v>
@@ -552,7 +449,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>3</v>
@@ -563,7 +460,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>4</v>
@@ -596,7 +493,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -604,7 +501,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>10</v>
@@ -615,7 +512,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>20</v>
@@ -626,7 +523,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>30</v>
@@ -637,7 +534,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>40</v>
@@ -667,10 +564,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -678,7 +575,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>100</v>
@@ -689,7 +586,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>10</v>
@@ -700,7 +597,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>1</v>
